--- a/2-file/fileTotal.xlsx
+++ b/2-file/fileTotal.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,12 +515,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fineTotal.xlsx</t>
+          <t>fileTotal.xlsx</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C:\codex\2026.5.31-python-learning-demo1\2-file\fineTotal.xlsx</t>
+          <t>C:\codex\2026.5.31-python-learning-demo1\2-file\fileTotal.xlsx</t>
         </is>
       </c>
     </row>
@@ -587,22 +587,10 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>~$fineTotal.xlsx</t>
+          <t>未付款订单.xlsx</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
-        <is>
-          <t>C:\codex\2026.5.31-python-learning-demo1\2-file\~$fineTotal.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>未付款订单.xlsx</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
         <is>
           <t>C:\codex\2026.5.31-python-learning-demo1\2-file\未付款订单.xlsx</t>
         </is>
